--- a/PV_ICE/baselines/SupportingMaterial/MaterialCompositionAnnual-Graph.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/MaterialCompositionAnnual-Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{160B6A70-25FA-4B44-8E92-E0BFA8BBFDDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49D4220-F954-4C48-A6A6-2E96375DD071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FB8D6CD-8546-4236-B63D-A974CB21DD58}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0FB8D6CD-8546-4236-B63D-A974CB21DD58}"/>
   </bookViews>
   <sheets>
     <sheet name="Silicon" sheetId="1" r:id="rId1"/>

--- a/PV_ICE/baselines/SupportingMaterial/MaterialCompositionAnnual-Graph.xlsx
+++ b/PV_ICE/baselines/SupportingMaterial/MaterialCompositionAnnual-Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hmirletz\Documents\GitHub\PV_ICE\PV_ICE\baselines\SupportingMaterial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49D4220-F954-4C48-A6A6-2E96375DD071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B87E4B-0985-49BF-97AE-1CC5244377F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{0FB8D6CD-8546-4236-B63D-A974CB21DD58}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0FB8D6CD-8546-4236-B63D-A974CB21DD58}"/>
   </bookViews>
   <sheets>
     <sheet name="Silicon" sheetId="1" r:id="rId1"/>
@@ -717,121 +717,121 @@
                   <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8080</c:v>
+                  <c:v>8045</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8160</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8292.7000000000007</c:v>
+                  <c:v>8180</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8225.6625000000004</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8158.8874999999998</c:v>
+                  <c:v>8135</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8289.75</c:v>
+                  <c:v>8208.375</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8350.15</c:v>
+                  <c:v>8253.5499999999993</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8607.5</c:v>
+                  <c:v>8450</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8975.5</c:v>
+                  <c:v>8764.1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9284.5874999999996</c:v>
+                  <c:v>9076.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9626.5</c:v>
+                  <c:v>9484.2124999999996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9805.4500000000007</c:v>
+                  <c:v>9654.375</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9977.4</c:v>
+                  <c:v>10176.9</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9940.2374999999993</c:v>
+                  <c:v>10240.36875</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9901.5</c:v>
+                  <c:v>10303.75</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>10008.405559999999</c:v>
+                  <c:v>10440.35</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10113.405559999999</c:v>
+                  <c:v>10571.35</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10216.5</c:v>
+                  <c:v>10553.79722</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10170.911109999999</c:v>
+                  <c:v>10535.85556</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10517.525</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10455.82778</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10393.936110000001</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>10125.011109999999</c:v>
+                  <c:v>10331.85</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3469,61 +3469,61 @@
                   <c:v>8000</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>8080</c:v>
+                  <c:v>8045</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>8160</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>8292.7000000000007</c:v>
+                  <c:v>8180</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>8225.6625000000004</c:v>
+                  <c:v>8090</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8158.8874999999998</c:v>
+                  <c:v>8135</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>8289.75</c:v>
+                  <c:v>8208.375</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>8350.15</c:v>
+                  <c:v>8253.5499999999993</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>8607.5</c:v>
+                  <c:v>8450</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>8975.5</c:v>
+                  <c:v>8764.1</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>9284.5874999999996</c:v>
+                  <c:v>9076.6</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>9626.5</c:v>
+                  <c:v>9484.2124999999996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>9805.4500000000007</c:v>
+                  <c:v>9654.375</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>9977.4</c:v>
+                  <c:v>10176.9</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>9940.2374999999993</c:v>
+                  <c:v>10240.36875</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>9901.5</c:v>
+                  <c:v>10303.75</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>10008.405559999999</c:v>
+                  <c:v>10440.35</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>10113.405559999999</c:v>
+                  <c:v>10571.35</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>10216.5</c:v>
+                  <c:v>10553.79722</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>10170.911109999999</c:v>
+                  <c:v>10535.85556</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13462,7 +13462,7 @@
         <v>2012</v>
       </c>
       <c r="B19">
-        <v>8080</v>
+        <v>8045</v>
       </c>
       <c r="C19">
         <v>1962.9861980000001</v>
@@ -13484,39 +13484,39 @@
       </c>
       <c r="I19">
         <f t="shared" si="1"/>
-        <v>11746.620733948999</v>
+        <v>11711.620733948999</v>
       </c>
       <c r="J19">
         <f t="shared" si="2"/>
-        <v>11.746620733948999</v>
+        <v>11.711620733948999</v>
       </c>
       <c r="L19" s="1">
         <f t="shared" si="3"/>
-        <v>68.785740026899219</v>
+        <v>68.692456686883645</v>
       </c>
       <c r="M19" s="1">
         <f t="shared" si="4"/>
-        <v>16.711071570794473</v>
+        <v>16.761012353395323</v>
       </c>
       <c r="N19" s="1">
         <f t="shared" si="5"/>
-        <v>3.5688561799599867</v>
+        <v>3.5795216522405671</v>
       </c>
       <c r="O19" s="1">
         <f t="shared" si="6"/>
-        <v>6.9962907930178536E-2</v>
+        <v>7.0171991013825361E-2</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="7"/>
-        <v>4.5766353760471563E-2</v>
+        <v>4.5903125810899496E-2</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="8"/>
-        <v>7.202071294895636</v>
+        <v>7.2235945751527115</v>
       </c>
       <c r="R19" s="1">
         <f t="shared" si="9"/>
-        <v>3.6165316657600401</v>
+        <v>3.6273396155030406</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
@@ -13524,7 +13524,7 @@
         <v>2013</v>
       </c>
       <c r="B20">
-        <v>8160</v>
+        <v>8090</v>
       </c>
       <c r="C20">
         <v>1619.458128</v>
@@ -13546,39 +13546,39 @@
       </c>
       <c r="I20">
         <f t="shared" si="1"/>
-        <v>11501.947299613999</v>
+        <v>11431.947299613999</v>
       </c>
       <c r="J20">
         <f t="shared" si="2"/>
-        <v>11.501947299613999</v>
+        <v>11.431947299613999</v>
       </c>
       <c r="L20" s="1">
         <f t="shared" si="3"/>
-        <v>70.944508677011981</v>
+        <v>70.766596345953758</v>
       </c>
       <c r="M20" s="1">
         <f t="shared" si="4"/>
-        <v>14.079860442886469</v>
+        <v>14.166074121551286</v>
       </c>
       <c r="N20" s="1">
         <f t="shared" si="5"/>
-        <v>3.6447741332814911</v>
+        <v>3.6670917824660982</v>
       </c>
       <c r="O20" s="1">
         <f t="shared" si="6"/>
-        <v>5.001582831276806E-2</v>
+        <v>5.0322084796474202E-2</v>
       </c>
       <c r="P20" s="1">
         <f t="shared" si="7"/>
-        <v>4.673991159897261E-2</v>
+        <v>4.702610901802811E-2</v>
       </c>
       <c r="Q20" s="1">
         <f t="shared" si="8"/>
-        <v>7.3552762672490379</v>
+        <v>7.4003140307387989</v>
       </c>
       <c r="R20" s="1">
         <f t="shared" si="9"/>
-        <v>3.8788247396592772</v>
+        <v>3.9025755254755587</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
@@ -13586,7 +13586,7 @@
         <v>2014</v>
       </c>
       <c r="B21">
-        <v>8292.7000000000007</v>
+        <v>8180</v>
       </c>
       <c r="C21">
         <v>1592.739726</v>
@@ -13608,39 +13608,39 @@
       </c>
       <c r="I21">
         <f t="shared" si="1"/>
-        <v>11613.587606342002</v>
+        <v>11500.887606342001</v>
       </c>
       <c r="J21">
         <f t="shared" si="2"/>
-        <v>11.613587606342001</v>
+        <v>11.500887606342001</v>
       </c>
       <c r="L21" s="1">
         <f t="shared" si="3"/>
-        <v>71.405153007770693</v>
+        <v>71.124945134575995</v>
       </c>
       <c r="M21" s="1">
         <f t="shared" si="4"/>
-        <v>13.714450521131209</v>
+        <v>13.848841763497507</v>
       </c>
       <c r="N21" s="1">
         <f t="shared" si="5"/>
-        <v>3.609737268189809</v>
+        <v>3.6451099632416812</v>
       </c>
       <c r="O21" s="1">
         <f t="shared" si="6"/>
-        <v>4.5996814447612042E-2</v>
+        <v>4.6447548440124706E-2</v>
       </c>
       <c r="P21" s="1">
         <f t="shared" si="7"/>
-        <v>4.6290605299814928E-2</v>
+        <v>4.6744218220474407E-2</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="8"/>
-        <v>7.3025668617410791</v>
+        <v>7.3741264937875997</v>
       </c>
       <c r="R21" s="1">
         <f t="shared" si="9"/>
-        <v>3.8758049214197716</v>
+        <v>3.9137848782365952</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
@@ -13648,7 +13648,7 @@
         <v>2015</v>
       </c>
       <c r="B22">
-        <v>8225.6625000000004</v>
+        <v>8090</v>
       </c>
       <c r="C22">
         <v>1495.242424</v>
@@ -13670,39 +13670,39 @@
       </c>
       <c r="I22">
         <f t="shared" si="1"/>
-        <v>11469.761856297</v>
+        <v>11334.099356297</v>
       </c>
       <c r="J22">
         <f t="shared" si="2"/>
-        <v>11.469761856297</v>
+        <v>11.334099356296999</v>
       </c>
       <c r="L22" s="1">
         <f t="shared" si="3"/>
-        <v>71.716070508334397</v>
+        <v>71.37752851535889</v>
       </c>
       <c r="M22" s="1">
         <f t="shared" si="4"/>
-        <v>13.036385957561086</v>
+        <v>13.192423826506101</v>
       </c>
       <c r="N22" s="1">
         <f t="shared" si="5"/>
-        <v>3.6550017799179026</v>
+        <v>3.6987500005202421</v>
       </c>
       <c r="O22" s="1">
         <f t="shared" si="6"/>
-        <v>3.9408425856012445E-2</v>
+        <v>3.9880121524510453E-2</v>
       </c>
       <c r="P22" s="1">
         <f t="shared" si="7"/>
-        <v>5.0464517681526662E-2</v>
+        <v>5.1068548263468447E-2</v>
       </c>
       <c r="Q22" s="1">
         <f t="shared" si="8"/>
-        <v>7.4132315095381767</v>
+        <v>7.501963528558635</v>
       </c>
       <c r="R22" s="1">
         <f t="shared" si="9"/>
-        <v>4.0894373011109044</v>
+        <v>4.1383854592681502</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
@@ -13710,7 +13710,7 @@
         <v>2016</v>
       </c>
       <c r="B23">
-        <v>8158.8874999999998</v>
+        <v>8135</v>
       </c>
       <c r="C23">
         <v>1412.526316</v>
@@ -13732,39 +13732,39 @@
       </c>
       <c r="I23">
         <f t="shared" si="1"/>
-        <v>11342.296926708999</v>
+        <v>11318.409426708999</v>
       </c>
       <c r="J23">
         <f t="shared" si="2"/>
-        <v>11.342296926708999</v>
+        <v>11.318409426708998</v>
       </c>
       <c r="L23" s="1">
         <f t="shared" si="3"/>
-        <v>71.933291402267358</v>
+        <v>71.874056621446826</v>
       </c>
       <c r="M23" s="1">
         <f t="shared" si="4"/>
-        <v>12.453617861773335</v>
+        <v>12.479901218865111</v>
       </c>
       <c r="N23" s="1">
         <f t="shared" si="5"/>
-        <v>3.6960767533145331</v>
+        <v>3.7038773222916945</v>
       </c>
       <c r="O23" s="1">
         <f t="shared" si="6"/>
-        <v>3.6145738693772286E-2</v>
+        <v>3.622202426540129E-2</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" si="7"/>
-        <v>5.466547067198884E-2</v>
+        <v>5.478084213289356E-2</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="8"/>
-        <v>7.5188474213877354</v>
+        <v>7.5347159468145133</v>
       </c>
       <c r="R23" s="1">
         <f t="shared" si="9"/>
-        <v>4.3073553518912782</v>
+        <v>4.3164460241835787</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
@@ -13772,7 +13772,7 @@
         <v>2017</v>
       </c>
       <c r="B24">
-        <v>8289.75</v>
+        <v>8208.375</v>
       </c>
       <c r="C24">
         <v>1379.8208959999999</v>
@@ -13794,39 +13794,39 @@
       </c>
       <c r="I24">
         <f t="shared" si="1"/>
-        <v>11428.487359453999</v>
+        <v>11347.112359453999</v>
       </c>
       <c r="J24">
         <f t="shared" si="2"/>
-        <v>11.428487359453998</v>
+        <v>11.347112359453998</v>
       </c>
       <c r="L24" s="1">
         <f t="shared" si="3"/>
-        <v>72.535846077149159</v>
+        <v>72.338888873001096</v>
       </c>
       <c r="M24" s="1">
         <f t="shared" si="4"/>
-        <v>12.073521653402096</v>
+        <v>12.160106045397388</v>
       </c>
       <c r="N24" s="1">
         <f t="shared" si="5"/>
-        <v>3.6682019834690398</v>
+        <v>3.6945082301112606</v>
       </c>
       <c r="O24" s="1">
         <f t="shared" si="6"/>
-        <v>3.5697696691462326E-2</v>
+        <v>3.5953700155272876E-2</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="7"/>
-        <v>6.3034063681583902E-2</v>
+        <v>6.3486107934747155E-2</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="8"/>
-        <v>7.4199670816323424</v>
+        <v>7.4731788417824712</v>
       </c>
       <c r="R24" s="1">
         <f t="shared" si="9"/>
-        <v>4.203731443974335</v>
+        <v>4.2338782016177818</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
@@ -13834,7 +13834,7 @@
         <v>2018</v>
       </c>
       <c r="B25">
-        <v>8350.15</v>
+        <v>8253.5499999999993</v>
       </c>
       <c r="C25">
         <v>1361.666667</v>
@@ -13856,39 +13856,39 @@
       </c>
       <c r="I25">
         <f t="shared" si="1"/>
-        <v>11456.294053672</v>
+        <v>11359.694053671998</v>
       </c>
       <c r="J25">
         <f t="shared" si="2"/>
-        <v>11.456294053672</v>
+        <v>11.359694053671998</v>
       </c>
       <c r="L25" s="1">
         <f t="shared" si="3"/>
-        <v>72.887008319445059</v>
+        <v>72.656446212405314</v>
       </c>
       <c r="M25" s="1">
         <f t="shared" si="4"/>
-        <v>11.885751715351224</v>
+        <v>11.986825178270044</v>
       </c>
       <c r="N25" s="1">
         <f t="shared" si="5"/>
-        <v>3.5862819719463443</v>
+        <v>3.616778817799164</v>
       </c>
       <c r="O25" s="1">
         <f t="shared" si="6"/>
-        <v>3.7658993840308783E-2</v>
+        <v>3.7979236514784513E-2</v>
       </c>
       <c r="P25" s="1">
         <f t="shared" si="7"/>
-        <v>6.5070955450995907E-2</v>
+        <v>6.562430259809926E-2</v>
       </c>
       <c r="Q25" s="1">
         <f t="shared" si="8"/>
-        <v>7.4103806695489887</v>
+        <v>7.4733966952708304</v>
       </c>
       <c r="R25" s="1">
         <f t="shared" si="9"/>
-        <v>4.1278473744170823</v>
+        <v>4.1629495571417836</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
@@ -13896,7 +13896,7 @@
         <v>2019</v>
       </c>
       <c r="B26">
-        <v>8607.5</v>
+        <v>8450</v>
       </c>
       <c r="C26">
         <v>1343.6470589999999</v>
@@ -13918,39 +13918,39 @@
       </c>
       <c r="I26">
         <f t="shared" si="1"/>
-        <v>11680.193239491997</v>
+        <v>11522.693239491997</v>
       </c>
       <c r="J26">
         <f t="shared" si="2"/>
-        <v>11.680193239491997</v>
+        <v>11.522693239491996</v>
       </c>
       <c r="L26" s="1">
         <f t="shared" si="3"/>
-        <v>73.693130100768471</v>
+        <v>73.333549929448054</v>
       </c>
       <c r="M26" s="1">
         <f t="shared" si="4"/>
-        <v>11.503637238269175</v>
+        <v>11.660876767897342</v>
       </c>
       <c r="N26" s="1">
         <f t="shared" si="5"/>
-        <v>3.4429281986561566</v>
+        <v>3.4899884804859149</v>
       </c>
       <c r="O26" s="1">
         <f t="shared" si="6"/>
-        <v>3.5293883478414896E-2</v>
+        <v>3.5776304257334753E-2</v>
       </c>
       <c r="P26" s="1">
         <f t="shared" si="7"/>
-        <v>7.0727596972182449E-2</v>
+        <v>7.1694349821675982E-2</v>
       </c>
       <c r="Q26" s="1">
         <f t="shared" si="8"/>
-        <v>7.2884924294028695</v>
+        <v>7.3881164959098733</v>
       </c>
       <c r="R26" s="1">
         <f t="shared" si="9"/>
-        <v>3.9657905524527637</v>
+        <v>4.0199976721798221</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
@@ -13958,7 +13958,7 @@
         <v>2020</v>
       </c>
       <c r="B27">
-        <v>8975.5</v>
+        <v>8764.1</v>
       </c>
       <c r="C27">
         <v>1343.6470589999999</v>
@@ -13980,39 +13980,39 @@
       </c>
       <c r="I27">
         <f t="shared" si="1"/>
-        <v>12008.284007142001</v>
+        <v>11796.884007142004</v>
       </c>
       <c r="J27">
         <f t="shared" si="2"/>
-        <v>12.008284007142002</v>
+        <v>11.796884007142003</v>
       </c>
       <c r="L27" s="1">
         <f t="shared" si="3"/>
-        <v>74.744234852055186</v>
+        <v>74.291651886159841</v>
       </c>
       <c r="M27" s="1">
         <f t="shared" si="4"/>
-        <v>11.189334447793351</v>
+        <v>11.38984716800247</v>
       </c>
       <c r="N27" s="1">
         <f t="shared" si="5"/>
-        <v>3.2939080485167493</v>
+        <v>3.3529348356780759</v>
       </c>
       <c r="O27" s="1">
         <f t="shared" si="6"/>
-        <v>2.8247456006058536E-2</v>
+        <v>2.8753650031198182E-2</v>
       </c>
       <c r="P27" s="1">
         <f t="shared" si="7"/>
-        <v>6.8496714394062991E-2</v>
+        <v>6.9724174578815024E-2</v>
       </c>
       <c r="Q27" s="1">
         <f t="shared" si="8"/>
-        <v>7.0738250319095339</v>
+        <v>7.2005878796954663</v>
       </c>
       <c r="R27" s="1">
         <f t="shared" si="9"/>
-        <v>3.6019534493250531</v>
+        <v>3.6665004058541091</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
@@ -14020,7 +14020,7 @@
         <v>2021</v>
       </c>
       <c r="B28">
-        <v>9284.5874999999996</v>
+        <v>9076.6</v>
       </c>
       <c r="C28">
         <v>1272.176471</v>
@@ -14042,39 +14042,39 @@
       </c>
       <c r="I28">
         <f t="shared" si="1"/>
-        <v>12176.010066372999</v>
+        <v>11968.022566373</v>
       </c>
       <c r="J28">
         <f t="shared" si="2"/>
-        <v>12.176010066372999</v>
+        <v>11.968022566373</v>
       </c>
       <c r="L28" s="1">
         <f t="shared" si="3"/>
-        <v>76.253119448723496</v>
+        <v>75.840431864682998</v>
       </c>
       <c r="M28" s="1">
         <f t="shared" si="4"/>
-        <v>10.448221248711214</v>
+        <v>10.6297967266078</v>
       </c>
       <c r="N28" s="1">
         <f t="shared" si="5"/>
-        <v>3.1943386863169594</v>
+        <v>3.2498518267573098</v>
       </c>
       <c r="O28" s="1">
         <f t="shared" si="6"/>
-        <v>2.8802664862157702E-2</v>
+        <v>2.9303214909151262E-2</v>
       </c>
       <c r="P28" s="1">
         <f t="shared" si="7"/>
-        <v>6.7921100220176625E-2</v>
+        <v>6.9101473983152015E-2</v>
       </c>
       <c r="Q28" s="1">
         <f t="shared" si="8"/>
-        <v>6.6500437794167926</v>
+        <v>6.7656122430373129</v>
       </c>
       <c r="R28" s="1">
         <f t="shared" si="9"/>
-        <v>3.3575530717492126</v>
+        <v>3.4159026500222818</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
@@ -14082,7 +14082,7 @@
         <v>2022</v>
       </c>
       <c r="B29">
-        <v>9626.5</v>
+        <v>9484.2124999999996</v>
       </c>
       <c r="C29">
         <v>1250.7352940000001</v>
@@ -14104,39 +14104,39 @@
       </c>
       <c r="I29">
         <f t="shared" si="1"/>
-        <v>12454.145746171002</v>
+        <v>12311.858246171001</v>
       </c>
       <c r="J29">
         <f t="shared" si="2"/>
-        <v>12.454145746171001</v>
+        <v>12.311858246171001</v>
       </c>
       <c r="L29" s="1">
         <f t="shared" si="3"/>
-        <v>77.295546368241645</v>
+        <v>77.033152188456995</v>
       </c>
       <c r="M29" s="1">
         <f t="shared" si="4"/>
-        <v>10.042722475642584</v>
+        <v>10.158785692557659</v>
       </c>
       <c r="N29" s="1">
         <f t="shared" si="5"/>
-        <v>3.085599027280916</v>
+        <v>3.1212591334010282</v>
       </c>
       <c r="O29" s="1">
         <f t="shared" si="6"/>
-        <v>2.5901994699169047E-2</v>
+        <v>2.6201342693360274E-2</v>
       </c>
       <c r="P29" s="1">
         <f t="shared" si="7"/>
-        <v>6.6763952899430226E-2</v>
+        <v>6.7535540401351971E-2</v>
       </c>
       <c r="Q29" s="1">
         <f t="shared" si="8"/>
-        <v>6.284714471409182</v>
+        <v>6.3573465869250292</v>
       </c>
       <c r="R29" s="1">
         <f t="shared" si="9"/>
-        <v>3.1987517098270684</v>
+        <v>3.2357195155645626</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
@@ -14144,7 +14144,7 @@
         <v>2023</v>
       </c>
       <c r="B30">
-        <v>9805.4500000000007</v>
+        <v>9654.375</v>
       </c>
       <c r="C30">
         <v>1229.294118</v>
@@ -14166,39 +14166,39 @@
       </c>
       <c r="I30">
         <f t="shared" si="1"/>
-        <v>12587.294738648001</v>
+        <v>12436.219738648</v>
       </c>
       <c r="J30">
         <f t="shared" si="2"/>
-        <v>12.587294738648001</v>
+        <v>12.436219738648001</v>
       </c>
       <c r="L30" s="1">
         <f t="shared" si="3"/>
-        <v>77.89958210713354</v>
+        <v>77.631106581344241</v>
       </c>
       <c r="M30" s="1">
         <f t="shared" si="4"/>
-        <v>9.7661502612279207</v>
+        <v>9.8847892995950097</v>
       </c>
       <c r="N30" s="1">
         <f t="shared" si="5"/>
-        <v>2.9789482790825264</v>
+        <v>3.0151364954955731</v>
       </c>
       <c r="O30" s="1">
         <f t="shared" si="6"/>
-        <v>2.396750620875698E-2</v>
+        <v>2.425866309377368E-2</v>
       </c>
       <c r="P30" s="1">
         <f t="shared" si="7"/>
-        <v>6.6627183792319772E-2</v>
+        <v>6.7436569763536056E-2</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="8"/>
-        <v>6.1834970592227574</v>
+        <v>6.2586140833550159</v>
       </c>
       <c r="R30" s="1">
         <f t="shared" si="9"/>
-        <v>3.0812276033321693</v>
+        <v>3.118658307352844</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
@@ -14206,7 +14206,7 @@
         <v>2024</v>
       </c>
       <c r="B31">
-        <v>9977.4</v>
+        <v>10176.9</v>
       </c>
       <c r="C31">
         <v>1215</v>
@@ -14228,39 +14228,39 @@
       </c>
       <c r="I31">
         <f t="shared" si="1"/>
-        <v>12707.636424315999</v>
+        <v>12907.136424315999</v>
       </c>
       <c r="J31">
         <f t="shared" si="2"/>
-        <v>12.707636424315998</v>
+        <v>12.907136424315999</v>
       </c>
       <c r="L31" s="1">
         <f t="shared" si="3"/>
-        <v>78.514994188126877</v>
+        <v>78.847078588458587</v>
       </c>
       <c r="M31" s="1">
         <f t="shared" si="4"/>
-        <v>9.5611800607948112</v>
+        <v>9.4133970546018126</v>
       </c>
       <c r="N31" s="1">
         <f t="shared" si="5"/>
-        <v>2.8774273026911978</v>
+        <v>2.8329521590175446</v>
       </c>
       <c r="O31" s="1">
         <f t="shared" si="6"/>
-        <v>2.0894399456686676E-2</v>
+        <v>2.0571443802188748E-2</v>
       </c>
       <c r="P31" s="1">
         <f t="shared" si="7"/>
-        <v>6.6560292705693094E-2</v>
+        <v>6.5531499179518712E-2</v>
       </c>
       <c r="Q31" s="1">
         <f t="shared" si="8"/>
-        <v>5.9495328222745787</v>
+        <v>5.857573478309817</v>
       </c>
       <c r="R31" s="1">
         <f t="shared" si="9"/>
-        <v>3.0094109339501696</v>
+        <v>2.9628957766305337</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
@@ -14268,7 +14268,7 @@
         <v>2025</v>
       </c>
       <c r="B32">
-        <v>9940.2374999999993</v>
+        <v>10240.36875</v>
       </c>
       <c r="C32">
         <v>1200.705882</v>
@@ -14290,39 +14290,39 @@
       </c>
       <c r="I32">
         <f t="shared" si="1"/>
-        <v>12609.195934104999</v>
+        <v>12909.327184104999</v>
       </c>
       <c r="J32">
         <f t="shared" si="2"/>
-        <v>12.609195934104999</v>
+        <v>12.909327184104999</v>
       </c>
       <c r="L32" s="1">
         <f t="shared" si="3"/>
-        <v>78.833238470931548</v>
+        <v>79.325348284678725</v>
       </c>
       <c r="M32" s="1">
         <f t="shared" si="4"/>
-        <v>9.5224619260008829</v>
+        <v>9.3010725104125136</v>
       </c>
       <c r="N32" s="1">
         <f t="shared" si="5"/>
-        <v>2.8537148750836723</v>
+        <v>2.7873683490108778</v>
       </c>
       <c r="O32" s="1">
         <f t="shared" si="6"/>
-        <v>1.8502676809785013E-2</v>
+        <v>1.8072504776799093E-2</v>
       </c>
       <c r="P32" s="1">
         <f t="shared" si="7"/>
-        <v>6.499552688235477E-2</v>
+        <v>6.348443428632633E-2</v>
       </c>
       <c r="Q32" s="1">
         <f t="shared" si="8"/>
-        <v>5.7135046815428518</v>
+        <v>5.5806703922342882</v>
       </c>
       <c r="R32" s="1">
         <f t="shared" si="9"/>
-        <v>2.993581842748902</v>
+        <v>2.9239835246004704</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
@@ -14330,7 +14330,7 @@
         <v>2026</v>
       </c>
       <c r="B33">
-        <v>9901.5</v>
+        <v>10303.75</v>
       </c>
       <c r="C33">
         <v>1191.176471</v>
@@ -14352,39 +14352,39 @@
       </c>
       <c r="I33">
         <f t="shared" si="1"/>
-        <v>12511.185262141002</v>
+        <v>12913.435262141002</v>
       </c>
       <c r="J33">
         <f t="shared" si="2"/>
-        <v>12.511185262141002</v>
+        <v>12.913435262141002</v>
       </c>
       <c r="L33" s="1">
         <f t="shared" si="3"/>
-        <v>79.141182809929759</v>
+        <v>79.790929298325807</v>
       </c>
       <c r="M33" s="1">
         <f t="shared" si="4"/>
-        <v>9.5208922739279895</v>
+        <v>9.224319066300156</v>
       </c>
       <c r="N33" s="1">
         <f t="shared" si="5"/>
-        <v>2.8295320753600581</v>
+        <v>2.7413929199603753</v>
       </c>
       <c r="O33" s="1">
         <f t="shared" si="6"/>
-        <v>1.7398333798052168E-2</v>
+        <v>1.6856380427148279E-2</v>
       </c>
       <c r="P33" s="1">
         <f t="shared" si="7"/>
-        <v>6.3403958144590059E-2</v>
+        <v>6.1428942074432988E-2</v>
       </c>
       <c r="Q33" s="1">
         <f t="shared" si="8"/>
-        <v>5.5317913706727753</v>
+        <v>5.3594775723934944</v>
       </c>
       <c r="R33" s="1">
         <f t="shared" si="9"/>
-        <v>2.8957991781667607</v>
+        <v>2.8055958205185765</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
@@ -14392,7 +14392,7 @@
         <v>2027</v>
       </c>
       <c r="B34">
-        <v>10008.405559999999</v>
+        <v>10440.35</v>
       </c>
       <c r="C34">
         <v>1181.6470589999999</v>
@@ -14414,39 +14414,39 @@
       </c>
       <c r="I34">
         <f t="shared" si="1"/>
-        <v>12574.685654875999</v>
+        <v>13006.630094876002</v>
       </c>
       <c r="J34">
         <f t="shared" si="2"/>
-        <v>12.574685654875999</v>
+        <v>13.006630094876002</v>
       </c>
       <c r="L34" s="1">
         <f t="shared" si="3"/>
-        <v>79.591695845844939</v>
+        <v>80.269446611793825</v>
       </c>
       <c r="M34" s="1">
         <f t="shared" si="4"/>
-        <v>9.3970306012524532</v>
+        <v>9.0849593659583903</v>
       </c>
       <c r="N34" s="1">
         <f t="shared" si="5"/>
-        <v>2.7720268821577738</v>
+        <v>2.6799690938955938</v>
       </c>
       <c r="O34" s="1">
         <f t="shared" si="6"/>
-        <v>1.6450230508926376E-2</v>
+        <v>1.5903925620325877E-2</v>
       </c>
       <c r="P34" s="1">
         <f t="shared" si="7"/>
-        <v>6.0993651932968594E-2</v>
+        <v>5.8968079695151193E-2</v>
       </c>
       <c r="Q34" s="1">
         <f t="shared" si="8"/>
-        <v>5.4099015257388432</v>
+        <v>5.2302410857982151</v>
       </c>
       <c r="R34" s="1">
         <f t="shared" si="9"/>
-        <v>2.7519012625641053</v>
+        <v>2.6605118372384911</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
@@ -14454,7 +14454,7 @@
         <v>2028</v>
       </c>
       <c r="B35">
-        <v>10113.405559999999</v>
+        <v>10571.35</v>
       </c>
       <c r="C35">
         <v>1172.117647</v>
@@ -14476,39 +14476,39 @@
       </c>
       <c r="I35">
         <f t="shared" si="1"/>
-        <v>12636.226040268997</v>
+        <v>13094.170480269</v>
       </c>
       <c r="J35">
         <f t="shared" si="2"/>
-        <v>12.636226040268998</v>
+        <v>13.094170480269</v>
       </c>
       <c r="L35" s="1">
         <f t="shared" ref="L35:L57" si="10">B35/$I35*100</f>
-        <v>80.035016212678528</v>
+        <v>80.73325466419945</v>
       </c>
       <c r="M35" s="1">
         <f t="shared" si="4"/>
-        <v>9.2758521671320793</v>
+        <v>8.9514463613117758</v>
       </c>
       <c r="N35" s="1">
         <f t="shared" si="5"/>
-        <v>2.7155206958666858</v>
+        <v>2.6205503725269255</v>
       </c>
       <c r="O35" s="1">
         <f t="shared" si="6"/>
-        <v>1.554667743153303E-2</v>
+        <v>1.5002961088373139E-2</v>
       </c>
       <c r="P35" s="1">
         <f t="shared" si="7"/>
-        <v>5.8522114462290657E-2</v>
+        <v>5.6475411543962739E-2</v>
       </c>
       <c r="Q35" s="1">
         <f t="shared" si="8"/>
-        <v>5.289026416353761</v>
+        <v>5.104052481270811</v>
       </c>
       <c r="R35" s="1">
         <f t="shared" si="9"/>
-        <v>2.610515716075128</v>
+        <v>2.5192177480587019</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
@@ -14516,7 +14516,7 @@
         <v>2029</v>
       </c>
       <c r="B36">
-        <v>10216.5</v>
+        <v>10553.79722</v>
       </c>
       <c r="C36">
         <v>1162.5882349999999</v>
@@ -14538,39 +14538,39 @@
       </c>
       <c r="I36">
         <f t="shared" si="1"/>
-        <v>12708.046736037</v>
+        <v>13045.343956037001</v>
       </c>
       <c r="J36">
         <f t="shared" si="2"/>
-        <v>12.708046736037</v>
+        <v>13.045343956037001</v>
       </c>
       <c r="L36" s="1">
         <f t="shared" si="10"/>
-        <v>80.393944185210103</v>
+        <v>80.90087356505471</v>
       </c>
       <c r="M36" s="1">
         <f t="shared" si="4"/>
-        <v>9.148441606711879</v>
+        <v>8.9119017399459857</v>
       </c>
       <c r="N36" s="1">
         <f t="shared" si="5"/>
-        <v>2.6574107493825063</v>
+        <v>2.588701387545401</v>
       </c>
       <c r="O36" s="1">
         <f t="shared" si="6"/>
-        <v>1.4486525287788647E-2</v>
+        <v>1.4111965236056966E-2</v>
       </c>
       <c r="P36" s="1">
         <f t="shared" si="7"/>
-        <v>5.60291717594079E-2</v>
+        <v>5.4580495209595264E-2</v>
       </c>
       <c r="Q36" s="1">
         <f t="shared" si="8"/>
-        <v>5.2738028685358831</v>
+        <v>5.1374447125240605</v>
       </c>
       <c r="R36" s="1">
         <f t="shared" si="9"/>
-        <v>2.4558848931124309</v>
+        <v>2.3923861344841866</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
@@ -14578,7 +14578,7 @@
         <v>2030</v>
       </c>
       <c r="B37">
-        <v>10170.911109999999</v>
+        <v>10535.85556</v>
       </c>
       <c r="C37">
         <v>1153.058824</v>
@@ -14600,39 +14600,39 @@
       </c>
       <c r="I37">
         <f t="shared" si="1"/>
-        <v>12634.534691269</v>
+        <v>12999.479141269001</v>
       </c>
       <c r="J37">
         <f t="shared" si="2"/>
-        <v>12.634534691269</v>
+        <v>12.999479141269001</v>
       </c>
       <c r="L37" s="1">
         <f t="shared" si="10"/>
-        <v>80.500876039610148</v>
+        <v>81.048290054577492</v>
       </c>
       <c r="M37" s="1">
         <f t="shared" si="4"/>
-        <v>9.1262468478305934</v>
+        <v>8.8700386490057408</v>
       </c>
       <c r="N37" s="1">
         <f t="shared" si="5"/>
-        <v>2.6544388708810862</v>
+        <v>2.5799187517851641</v>
       </c>
       <c r="O37" s="1">
         <f t="shared" si="6"/>
-        <v>1.3514859159633179E-2</v>
+        <v>1.3135446047058397E-2</v>
       </c>
       <c r="P37" s="1">
         <f t="shared" si="7"/>
-        <v>5.4180388651198133E-2</v>
+        <v>5.2659340621333178E-2</v>
       </c>
       <c r="Q37" s="1">
         <f t="shared" si="8"/>
-        <v>5.3167081314375721</v>
+        <v>5.1674480646493421</v>
       </c>
       <c r="R37" s="1">
         <f t="shared" si="9"/>
-        <v>2.3340348624297547</v>
+        <v>2.2685096933138551</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
@@ -14640,7 +14640,7 @@
         <v>2031</v>
       </c>
       <c r="B38">
-        <v>10125.011109999999</v>
+        <v>10517.525</v>
       </c>
       <c r="C38">
         <v>1143.5294120000001</v>
@@ -14662,39 +14662,39 @@
       </c>
       <c r="I38">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12953.541977141</v>
       </c>
       <c r="J38">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.953541977141001</v>
       </c>
       <c r="L38" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>81.194201698347698</v>
       </c>
       <c r="M38" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.8279284076739497</v>
       </c>
       <c r="N38" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.5710882829401029</v>
       </c>
       <c r="O38" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.218296234176647E-2</v>
       </c>
       <c r="P38" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.2846086515024898E-2</v>
       </c>
       <c r="Q38" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.1976929127812355</v>
       </c>
       <c r="R38" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1440596494002229</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
@@ -14702,7 +14702,7 @@
         <v>2032</v>
       </c>
       <c r="B39">
-        <v>10125.011109999999</v>
+        <v>10455.82778</v>
       </c>
       <c r="C39">
         <v>1143.5294120000001</v>
@@ -14724,39 +14724,39 @@
       </c>
       <c r="I39">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12891.844757141</v>
       </c>
       <c r="J39">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.891844757141</v>
       </c>
       <c r="L39" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>81.104201741246911</v>
       </c>
       <c r="M39" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.870176716692006</v>
       </c>
       <c r="N39" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.5833928834391213</v>
       </c>
       <c r="O39" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2241267023680618E-2</v>
       </c>
       <c r="P39" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3098994976713478E-2</v>
       </c>
       <c r="Q39" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2225678014549199</v>
       </c>
       <c r="R39" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1543205951666455</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.35">
@@ -14764,7 +14764,7 @@
         <v>2033</v>
       </c>
       <c r="B40">
-        <v>10125.011109999999</v>
+        <v>10393.936110000001</v>
       </c>
       <c r="C40">
         <v>1143.5294120000001</v>
@@ -14786,39 +14786,39 @@
       </c>
       <c r="I40">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12829.953087141001</v>
       </c>
       <c r="J40">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.829953087141</v>
       </c>
       <c r="L40" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>81.013048445340516</v>
       </c>
       <c r="M40" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9129664327932616</v>
       </c>
       <c r="N40" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.5958551659382221</v>
       </c>
       <c r="O40" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.230031887319758E-2</v>
       </c>
       <c r="P40" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3355144430426153E-2</v>
       </c>
       <c r="Q40" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2477614588849093</v>
       </c>
       <c r="R40" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1647130337394644</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.35">
@@ -14826,7 +14826,7 @@
         <v>2034</v>
       </c>
       <c r="B41">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C41">
         <v>1143.5294120000001</v>
@@ -14848,39 +14848,39 @@
       </c>
       <c r="I41">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J41">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L41" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M41" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N41" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O41" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P41" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q41" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R41" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.35">
@@ -14888,7 +14888,7 @@
         <v>2035</v>
       </c>
       <c r="B42">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C42">
         <v>1143.5294120000001</v>
@@ -14910,39 +14910,39 @@
       </c>
       <c r="I42">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J42">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L42" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M42" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N42" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O42" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P42" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q42" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R42" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.35">
@@ -14950,7 +14950,7 @@
         <v>2036</v>
       </c>
       <c r="B43">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C43">
         <v>1143.5294120000001</v>
@@ -14972,39 +14972,39 @@
       </c>
       <c r="I43">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J43">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L43" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M43" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N43" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O43" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P43" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q43" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R43" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.35">
@@ -15012,7 +15012,7 @@
         <v>2037</v>
       </c>
       <c r="B44">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C44">
         <v>1143.5294120000001</v>
@@ -15034,39 +15034,39 @@
       </c>
       <c r="I44">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J44">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L44" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M44" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N44" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O44" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P44" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q44" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R44" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.35">
@@ -15074,7 +15074,7 @@
         <v>2038</v>
       </c>
       <c r="B45">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C45">
         <v>1143.5294120000001</v>
@@ -15096,39 +15096,39 @@
       </c>
       <c r="I45">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J45">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L45" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M45" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N45" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O45" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P45" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q45" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R45" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.35">
@@ -15136,7 +15136,7 @@
         <v>2039</v>
       </c>
       <c r="B46">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C46">
         <v>1143.5294120000001</v>
@@ -15158,39 +15158,39 @@
       </c>
       <c r="I46">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J46">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L46" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M46" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N46" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O46" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P46" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q46" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R46" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.35">
@@ -15198,7 +15198,7 @@
         <v>2040</v>
       </c>
       <c r="B47">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C47">
         <v>1143.5294120000001</v>
@@ -15220,39 +15220,39 @@
       </c>
       <c r="I47">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J47">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L47" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M47" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N47" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O47" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P47" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q47" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R47" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
@@ -15260,7 +15260,7 @@
         <v>2041</v>
       </c>
       <c r="B48">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C48">
         <v>1143.5294120000001</v>
@@ -15282,39 +15282,39 @@
       </c>
       <c r="I48">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J48">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L48" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M48" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N48" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O48" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P48" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q48" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R48" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.35">
@@ -15322,7 +15322,7 @@
         <v>2042</v>
       </c>
       <c r="B49">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C49">
         <v>1143.5294120000001</v>
@@ -15344,39 +15344,39 @@
       </c>
       <c r="I49">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J49">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L49" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M49" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N49" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O49" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P49" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q49" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R49" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="50" spans="1:18" x14ac:dyDescent="0.35">
@@ -15384,7 +15384,7 @@
         <v>2043</v>
       </c>
       <c r="B50">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C50">
         <v>1143.5294120000001</v>
@@ -15406,39 +15406,39 @@
       </c>
       <c r="I50">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J50">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L50" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M50" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N50" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O50" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P50" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q50" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R50" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.35">
@@ -15446,7 +15446,7 @@
         <v>2044</v>
       </c>
       <c r="B51">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C51">
         <v>1143.5294120000001</v>
@@ -15468,39 +15468,39 @@
       </c>
       <c r="I51">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J51">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L51" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M51" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N51" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O51" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P51" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q51" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R51" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.35">
@@ -15508,7 +15508,7 @@
         <v>2045</v>
       </c>
       <c r="B52">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C52">
         <v>1143.5294120000001</v>
@@ -15530,39 +15530,39 @@
       </c>
       <c r="I52">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J52">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L52" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M52" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N52" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O52" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P52" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q52" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R52" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
@@ -15570,7 +15570,7 @@
         <v>2046</v>
       </c>
       <c r="B53">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C53">
         <v>1143.5294120000001</v>
@@ -15592,39 +15592,39 @@
       </c>
       <c r="I53">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J53">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L53" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M53" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N53" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O53" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P53" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q53" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R53" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.35">
@@ -15632,7 +15632,7 @@
         <v>2047</v>
       </c>
       <c r="B54">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C54">
         <v>1143.5294120000001</v>
@@ -15654,39 +15654,39 @@
       </c>
       <c r="I54">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J54">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L54" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M54" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N54" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O54" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P54" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q54" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R54" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.35">
@@ -15694,7 +15694,7 @@
         <v>2048</v>
       </c>
       <c r="B55">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C55">
         <v>1143.5294120000001</v>
@@ -15716,39 +15716,39 @@
       </c>
       <c r="I55">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J55">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L55" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M55" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N55" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O55" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P55" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q55" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R55" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.35">
@@ -15756,7 +15756,7 @@
         <v>2049</v>
       </c>
       <c r="B56">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C56">
         <v>1143.5294120000001</v>
@@ -15778,39 +15778,39 @@
       </c>
       <c r="I56">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J56">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L56" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M56" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N56" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O56" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P56" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q56" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R56" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.35">
@@ -15818,7 +15818,7 @@
         <v>2050</v>
       </c>
       <c r="B57">
-        <v>10125.011109999999</v>
+        <v>10331.85</v>
       </c>
       <c r="C57">
         <v>1143.5294120000001</v>
@@ -15840,39 +15840,39 @@
       </c>
       <c r="I57">
         <f t="shared" si="1"/>
-        <v>12561.028087141</v>
+        <v>12767.866977141</v>
       </c>
       <c r="J57">
         <f t="shared" si="2"/>
-        <v>12.561028087140999</v>
+        <v>12.767866977141001</v>
       </c>
       <c r="L57" s="1">
         <f t="shared" si="10"/>
-        <v>80.606547806108281</v>
+        <v>80.920720888600002</v>
       </c>
       <c r="M57" s="1">
         <f t="shared" si="4"/>
-        <v>9.1037883528869443</v>
+        <v>8.9563073773193462</v>
       </c>
       <c r="N57" s="1">
         <f t="shared" si="5"/>
-        <v>2.6514310587438903</v>
+        <v>2.6084779908521289</v>
       </c>
       <c r="O57" s="1">
         <f t="shared" si="6"/>
-        <v>1.2563662226148202E-2</v>
+        <v>1.2360131444237336E-2</v>
       </c>
       <c r="P57" s="1">
         <f t="shared" si="7"/>
-        <v>5.4497449989844605E-2</v>
+        <v>5.3614593669058117E-2</v>
       </c>
       <c r="Q57" s="1">
         <f t="shared" si="8"/>
-        <v>5.3601132696236631</v>
+        <v>5.2732796676642932</v>
       </c>
       <c r="R57" s="1">
         <f t="shared" si="9"/>
-        <v>2.2110584004212201</v>
+        <v>2.1752393504509246</v>
       </c>
     </row>
   </sheetData>
